--- a/final/task_2/Climate-Final.xlsx
+++ b/final/task_2/Climate-Final.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Athina\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD567AAD-A9E0-4035-9189-5A45DFA48468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83D13B3D-3D84-42F8-AC0B-83A029C17F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="452">
   <si>
     <t>post_id</t>
   </si>
@@ -1539,6 +1552,12 @@
   </si>
   <si>
     <t>Athina</t>
+  </si>
+  <si>
+    <t>ai_opinion</t>
+  </si>
+  <si>
+    <t>Alex</t>
   </si>
 </sst>
 </file>
@@ -1920,13 +1939,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F221"/>
+  <dimension ref="A1:H221"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="62.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1934,19 +1955,25 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1957,16 +1984,22 @@
         <v>442</v>
       </c>
       <c r="D2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E2" t="s">
         <v>442</v>
       </c>
       <c r="F2" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G2" t="s">
+        <v>442</v>
+      </c>
+      <c r="H2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1974,19 +2007,25 @@
         <v>223</v>
       </c>
       <c r="C3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E3" t="s">
         <v>443</v>
       </c>
       <c r="F3" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G3" t="s">
+        <v>443</v>
+      </c>
+      <c r="H3" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1997,16 +2036,22 @@
         <v>442</v>
       </c>
       <c r="D4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E4" t="s">
         <v>442</v>
       </c>
       <c r="F4" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G4" t="s">
+        <v>442</v>
+      </c>
+      <c r="H4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -2014,7 +2059,7 @@
         <v>225</v>
       </c>
       <c r="C5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D5" t="s">
         <v>442</v>
@@ -2025,8 +2070,14 @@
       <c r="F5" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>442</v>
+      </c>
+      <c r="H5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -2034,7 +2085,7 @@
         <v>226</v>
       </c>
       <c r="C6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D6" t="s">
         <v>442</v>
@@ -2045,8 +2096,14 @@
       <c r="F6" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>442</v>
+      </c>
+      <c r="H6" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -2057,16 +2114,22 @@
         <v>443</v>
       </c>
       <c r="D7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E7" t="s">
         <v>443</v>
       </c>
       <c r="F7" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G7" t="s">
+        <v>443</v>
+      </c>
+      <c r="H7" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2077,16 +2140,22 @@
         <v>443</v>
       </c>
       <c r="D8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E8" t="s">
         <v>443</v>
       </c>
       <c r="F8" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G8" t="s">
+        <v>443</v>
+      </c>
+      <c r="H8" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2097,16 +2166,22 @@
         <v>443</v>
       </c>
       <c r="D9" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F9" t="s">
+        <v>444</v>
+      </c>
+      <c r="G9" t="s">
+        <v>442</v>
+      </c>
+      <c r="H9" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -2125,8 +2200,14 @@
       <c r="F10" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>442</v>
+      </c>
+      <c r="H10" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2137,16 +2218,22 @@
         <v>443</v>
       </c>
       <c r="D11" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E11" t="s">
         <v>443</v>
       </c>
       <c r="F11" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G11" t="s">
+        <v>443</v>
+      </c>
+      <c r="H11" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -2165,8 +2252,14 @@
       <c r="F12" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>442</v>
+      </c>
+      <c r="H12" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2174,7 +2267,7 @@
         <v>233</v>
       </c>
       <c r="C13" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D13" t="s">
         <v>442</v>
@@ -2185,8 +2278,14 @@
       <c r="F13" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>442</v>
+      </c>
+      <c r="H13" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -2194,7 +2293,7 @@
         <v>234</v>
       </c>
       <c r="C14" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D14" t="s">
         <v>442</v>
@@ -2205,8 +2304,14 @@
       <c r="F14" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>442</v>
+      </c>
+      <c r="H14" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -2214,19 +2319,25 @@
         <v>235</v>
       </c>
       <c r="C15" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D15" t="s">
         <v>444</v>
       </c>
       <c r="E15" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F15" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>443</v>
+      </c>
+      <c r="H15" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -2245,8 +2356,14 @@
       <c r="F16" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>442</v>
+      </c>
+      <c r="H16" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -2257,16 +2374,22 @@
         <v>443</v>
       </c>
       <c r="D17" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E17" t="s">
         <v>443</v>
       </c>
       <c r="F17" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G17" t="s">
+        <v>443</v>
+      </c>
+      <c r="H17" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -2285,8 +2408,14 @@
       <c r="F18" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>442</v>
+      </c>
+      <c r="H18" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -2297,16 +2426,22 @@
         <v>443</v>
       </c>
       <c r="D19" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E19" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F19" t="s">
+        <v>444</v>
+      </c>
+      <c r="G19" t="s">
+        <v>442</v>
+      </c>
+      <c r="H19" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -2317,16 +2452,22 @@
         <v>443</v>
       </c>
       <c r="D20" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E20" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F20" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>444</v>
+      </c>
+      <c r="H20" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -2345,8 +2486,14 @@
       <c r="F21" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G21" t="s">
+        <v>442</v>
+      </c>
+      <c r="H21" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -2360,13 +2507,19 @@
         <v>444</v>
       </c>
       <c r="E22" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F22" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22" t="s">
+        <v>443</v>
+      </c>
+      <c r="H22" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -2374,19 +2527,25 @@
         <v>243</v>
       </c>
       <c r="C23" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D23" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E23" t="s">
         <v>442</v>
       </c>
       <c r="F23" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G23" t="s">
+        <v>442</v>
+      </c>
+      <c r="H23" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -2394,7 +2553,7 @@
         <v>244</v>
       </c>
       <c r="C24" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D24" t="s">
         <v>442</v>
@@ -2405,8 +2564,14 @@
       <c r="F24" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G24" t="s">
+        <v>442</v>
+      </c>
+      <c r="H24" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -2417,16 +2582,22 @@
         <v>443</v>
       </c>
       <c r="D25" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E25" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F25" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G25" t="s">
+        <v>444</v>
+      </c>
+      <c r="H25" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -2445,8 +2616,14 @@
       <c r="F26" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G26" t="s">
+        <v>442</v>
+      </c>
+      <c r="H26" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -2457,16 +2634,22 @@
         <v>442</v>
       </c>
       <c r="D27" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E27" t="s">
         <v>442</v>
       </c>
       <c r="F27" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G27" t="s">
+        <v>442</v>
+      </c>
+      <c r="H27" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -2474,7 +2657,7 @@
         <v>248</v>
       </c>
       <c r="C28" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D28" t="s">
         <v>442</v>
@@ -2485,8 +2668,14 @@
       <c r="F28" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G28" t="s">
+        <v>442</v>
+      </c>
+      <c r="H28" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -2497,16 +2686,22 @@
         <v>443</v>
       </c>
       <c r="D29" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E29" t="s">
         <v>443</v>
       </c>
       <c r="F29" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G29" t="s">
+        <v>443</v>
+      </c>
+      <c r="H29" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -2517,16 +2712,22 @@
         <v>443</v>
       </c>
       <c r="D30" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E30" t="s">
         <v>443</v>
       </c>
       <c r="F30" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G30" t="s">
+        <v>443</v>
+      </c>
+      <c r="H30" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -2545,8 +2746,14 @@
       <c r="F31" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G31" t="s">
+        <v>444</v>
+      </c>
+      <c r="H31" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>32</v>
       </c>
@@ -2557,16 +2764,22 @@
         <v>443</v>
       </c>
       <c r="D32" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E32" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F32" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G32" t="s">
+        <v>444</v>
+      </c>
+      <c r="H32" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -2585,8 +2798,14 @@
       <c r="F33" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G33" t="s">
+        <v>442</v>
+      </c>
+      <c r="H33" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -2597,16 +2816,22 @@
         <v>443</v>
       </c>
       <c r="D34" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E34" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F34" t="s">
+        <v>444</v>
+      </c>
+      <c r="G34" t="s">
+        <v>442</v>
+      </c>
+      <c r="H34" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -2617,16 +2842,22 @@
         <v>442</v>
       </c>
       <c r="D35" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E35" t="s">
         <v>442</v>
       </c>
       <c r="F35" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G35" t="s">
+        <v>442</v>
+      </c>
+      <c r="H35" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -2637,16 +2868,22 @@
         <v>442</v>
       </c>
       <c r="D36" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E36" t="s">
         <v>442</v>
       </c>
       <c r="F36" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G36" t="s">
+        <v>442</v>
+      </c>
+      <c r="H36" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -2657,16 +2894,22 @@
         <v>443</v>
       </c>
       <c r="D37" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E37" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F37" t="s">
+        <v>444</v>
+      </c>
+      <c r="G37" t="s">
+        <v>442</v>
+      </c>
+      <c r="H37" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -2677,16 +2920,22 @@
         <v>443</v>
       </c>
       <c r="D38" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E38" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F38" t="s">
+        <v>444</v>
+      </c>
+      <c r="G38" t="s">
+        <v>442</v>
+      </c>
+      <c r="H38" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -2705,8 +2954,14 @@
       <c r="F39" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G39" t="s">
+        <v>442</v>
+      </c>
+      <c r="H39" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -2725,8 +2980,14 @@
       <c r="F40" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G40" t="s">
+        <v>444</v>
+      </c>
+      <c r="H40" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>41</v>
       </c>
@@ -2745,8 +3006,14 @@
       <c r="F41" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G41" t="s">
+        <v>444</v>
+      </c>
+      <c r="H41" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>42</v>
       </c>
@@ -2757,16 +3024,22 @@
         <v>442</v>
       </c>
       <c r="D42" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E42" t="s">
         <v>442</v>
       </c>
       <c r="F42" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G42" t="s">
+        <v>442</v>
+      </c>
+      <c r="H42" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>43</v>
       </c>
@@ -2780,13 +3053,19 @@
         <v>444</v>
       </c>
       <c r="E43" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F43" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G43" t="s">
+        <v>443</v>
+      </c>
+      <c r="H43" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -2805,8 +3084,14 @@
       <c r="F44" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G44" t="s">
+        <v>442</v>
+      </c>
+      <c r="H44" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>45</v>
       </c>
@@ -2820,13 +3105,19 @@
         <v>444</v>
       </c>
       <c r="E45" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F45" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G45" t="s">
+        <v>443</v>
+      </c>
+      <c r="H45" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>46</v>
       </c>
@@ -2845,8 +3136,14 @@
       <c r="F46" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G46" t="s">
+        <v>442</v>
+      </c>
+      <c r="H46" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>47</v>
       </c>
@@ -2860,13 +3157,19 @@
         <v>444</v>
       </c>
       <c r="E47" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F47" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G47" t="s">
+        <v>443</v>
+      </c>
+      <c r="H47" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>48</v>
       </c>
@@ -2885,8 +3188,14 @@
       <c r="F48" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G48" t="s">
+        <v>442</v>
+      </c>
+      <c r="H48" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>49</v>
       </c>
@@ -2905,8 +3214,14 @@
       <c r="F49" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G49" t="s">
+        <v>442</v>
+      </c>
+      <c r="H49" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>50</v>
       </c>
@@ -2920,13 +3235,19 @@
         <v>444</v>
       </c>
       <c r="E50" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F50" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G50" t="s">
+        <v>443</v>
+      </c>
+      <c r="H50" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>51</v>
       </c>
@@ -2937,16 +3258,22 @@
         <v>442</v>
       </c>
       <c r="D51" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E51" t="s">
         <v>442</v>
       </c>
       <c r="F51" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G51" t="s">
+        <v>442</v>
+      </c>
+      <c r="H51" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>52</v>
       </c>
@@ -2954,19 +3281,25 @@
         <v>272</v>
       </c>
       <c r="C52" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D52" t="s">
         <v>444</v>
       </c>
       <c r="E52" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F52" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G52" t="s">
+        <v>443</v>
+      </c>
+      <c r="H52" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>53</v>
       </c>
@@ -2985,8 +3318,14 @@
       <c r="F53" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G53" t="s">
+        <v>442</v>
+      </c>
+      <c r="H53" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>54</v>
       </c>
@@ -2994,19 +3333,25 @@
         <v>274</v>
       </c>
       <c r="C54" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D54" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E54" t="s">
         <v>443</v>
       </c>
       <c r="F54" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G54" t="s">
+        <v>443</v>
+      </c>
+      <c r="H54" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>55</v>
       </c>
@@ -3017,16 +3362,22 @@
         <v>443</v>
       </c>
       <c r="D55" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E55" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F55" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G55" t="s">
+        <v>444</v>
+      </c>
+      <c r="H55" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>56</v>
       </c>
@@ -3045,8 +3396,14 @@
       <c r="F56" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G56" t="s">
+        <v>444</v>
+      </c>
+      <c r="H56" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>57</v>
       </c>
@@ -3065,8 +3422,14 @@
       <c r="F57" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G57" t="s">
+        <v>442</v>
+      </c>
+      <c r="H57" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>58</v>
       </c>
@@ -3077,16 +3440,22 @@
         <v>443</v>
       </c>
       <c r="D58" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E58" t="s">
         <v>443</v>
       </c>
       <c r="F58" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G58" t="s">
+        <v>443</v>
+      </c>
+      <c r="H58" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>59</v>
       </c>
@@ -3094,7 +3463,7 @@
         <v>279</v>
       </c>
       <c r="C59" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D59" t="s">
         <v>442</v>
@@ -3105,8 +3474,14 @@
       <c r="F59" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G59" t="s">
+        <v>442</v>
+      </c>
+      <c r="H59" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>60</v>
       </c>
@@ -3114,19 +3489,25 @@
         <v>280</v>
       </c>
       <c r="C60" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D60" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E60" t="s">
         <v>442</v>
       </c>
       <c r="F60" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G60" t="s">
+        <v>442</v>
+      </c>
+      <c r="H60" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>61</v>
       </c>
@@ -3145,8 +3526,14 @@
       <c r="F61" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G61" t="s">
+        <v>442</v>
+      </c>
+      <c r="H61" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>62</v>
       </c>
@@ -3165,8 +3552,14 @@
       <c r="F62" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G62" t="s">
+        <v>442</v>
+      </c>
+      <c r="H62" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>63</v>
       </c>
@@ -3177,16 +3570,22 @@
         <v>443</v>
       </c>
       <c r="D63" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E63" t="s">
         <v>443</v>
       </c>
       <c r="F63" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G63" t="s">
+        <v>443</v>
+      </c>
+      <c r="H63" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>64</v>
       </c>
@@ -3205,8 +3604,14 @@
       <c r="F64" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G64" t="s">
+        <v>442</v>
+      </c>
+      <c r="H64" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>65</v>
       </c>
@@ -3225,8 +3630,14 @@
       <c r="F65" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G65" t="s">
+        <v>442</v>
+      </c>
+      <c r="H65" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>66</v>
       </c>
@@ -3237,16 +3648,22 @@
         <v>443</v>
       </c>
       <c r="D66" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E66" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F66" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G66" t="s">
+        <v>444</v>
+      </c>
+      <c r="H66" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>67</v>
       </c>
@@ -3257,16 +3674,22 @@
         <v>443</v>
       </c>
       <c r="D67" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E67" t="s">
         <v>443</v>
       </c>
       <c r="F67" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G67" t="s">
+        <v>443</v>
+      </c>
+      <c r="H67" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>68</v>
       </c>
@@ -3277,16 +3700,22 @@
         <v>443</v>
       </c>
       <c r="D68" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E68" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F68" t="s">
+        <v>444</v>
+      </c>
+      <c r="G68" t="s">
+        <v>442</v>
+      </c>
+      <c r="H68" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>69</v>
       </c>
@@ -3305,8 +3734,14 @@
       <c r="F69" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G69" t="s">
+        <v>442</v>
+      </c>
+      <c r="H69" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>70</v>
       </c>
@@ -3317,16 +3752,22 @@
         <v>443</v>
       </c>
       <c r="D70" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E70" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F70" t="s">
+        <v>444</v>
+      </c>
+      <c r="G70" t="s">
+        <v>442</v>
+      </c>
+      <c r="H70" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>71</v>
       </c>
@@ -3337,16 +3778,22 @@
         <v>442</v>
       </c>
       <c r="D71" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E71" t="s">
         <v>442</v>
       </c>
       <c r="F71" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G71" t="s">
+        <v>442</v>
+      </c>
+      <c r="H71" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>72</v>
       </c>
@@ -3357,16 +3804,22 @@
         <v>443</v>
       </c>
       <c r="D72" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E72" t="s">
         <v>443</v>
       </c>
       <c r="F72" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G72" t="s">
+        <v>443</v>
+      </c>
+      <c r="H72" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>73</v>
       </c>
@@ -3377,16 +3830,22 @@
         <v>442</v>
       </c>
       <c r="D73" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E73" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F73" t="s">
+        <v>443</v>
+      </c>
+      <c r="G73" t="s">
+        <v>443</v>
+      </c>
+      <c r="H73" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>74</v>
       </c>
@@ -3400,13 +3859,19 @@
         <v>444</v>
       </c>
       <c r="E74" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F74" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G74" t="s">
+        <v>443</v>
+      </c>
+      <c r="H74" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>75</v>
       </c>
@@ -3417,16 +3882,22 @@
         <v>443</v>
       </c>
       <c r="D75" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E75" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F75" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G75" t="s">
+        <v>444</v>
+      </c>
+      <c r="H75" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>76</v>
       </c>
@@ -3445,8 +3916,14 @@
       <c r="F76" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G76" t="s">
+        <v>442</v>
+      </c>
+      <c r="H76" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>77</v>
       </c>
@@ -3465,8 +3942,14 @@
       <c r="F77" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G77" t="s">
+        <v>444</v>
+      </c>
+      <c r="H77" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>78</v>
       </c>
@@ -3477,16 +3960,22 @@
         <v>443</v>
       </c>
       <c r="D78" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E78" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F78" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G78" t="s">
+        <v>444</v>
+      </c>
+      <c r="H78" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>79</v>
       </c>
@@ -3497,16 +3986,22 @@
         <v>443</v>
       </c>
       <c r="D79" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E79" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F79" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G79" t="s">
+        <v>444</v>
+      </c>
+      <c r="H79" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>80</v>
       </c>
@@ -3517,16 +4012,22 @@
         <v>442</v>
       </c>
       <c r="D80" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E80" t="s">
         <v>442</v>
       </c>
       <c r="F80" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G80" t="s">
+        <v>442</v>
+      </c>
+      <c r="H80" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>81</v>
       </c>
@@ -3537,16 +4038,22 @@
         <v>442</v>
       </c>
       <c r="D81" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E81" t="s">
         <v>442</v>
       </c>
       <c r="F81" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G81" t="s">
+        <v>442</v>
+      </c>
+      <c r="H81" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>82</v>
       </c>
@@ -3557,16 +4064,22 @@
         <v>443</v>
       </c>
       <c r="D82" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E82" t="s">
         <v>443</v>
       </c>
       <c r="F82" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G82" t="s">
+        <v>443</v>
+      </c>
+      <c r="H82" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>83</v>
       </c>
@@ -3585,8 +4098,14 @@
       <c r="F83" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G83" t="s">
+        <v>442</v>
+      </c>
+      <c r="H83" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>84</v>
       </c>
@@ -3597,16 +4116,22 @@
         <v>443</v>
       </c>
       <c r="D84" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E84" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F84" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G84" t="s">
+        <v>444</v>
+      </c>
+      <c r="H84" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>85</v>
       </c>
@@ -3625,8 +4150,14 @@
       <c r="F85" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G85" t="s">
+        <v>442</v>
+      </c>
+      <c r="H85" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>86</v>
       </c>
@@ -3637,16 +4168,22 @@
         <v>443</v>
       </c>
       <c r="D86" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E86" t="s">
         <v>443</v>
       </c>
       <c r="F86" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G86" t="s">
+        <v>443</v>
+      </c>
+      <c r="H86" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>87</v>
       </c>
@@ -3665,8 +4202,14 @@
       <c r="F87" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G87" t="s">
+        <v>442</v>
+      </c>
+      <c r="H87" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>88</v>
       </c>
@@ -3677,16 +4220,22 @@
         <v>443</v>
       </c>
       <c r="D88" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E88" t="s">
         <v>443</v>
       </c>
       <c r="F88" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G88" t="s">
+        <v>443</v>
+      </c>
+      <c r="H88" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>89</v>
       </c>
@@ -3705,8 +4254,14 @@
       <c r="F89" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G89" t="s">
+        <v>442</v>
+      </c>
+      <c r="H89" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>90</v>
       </c>
@@ -3717,16 +4272,22 @@
         <v>443</v>
       </c>
       <c r="D90" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E90" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F90" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G90" t="s">
+        <v>442</v>
+      </c>
+      <c r="H90" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>91</v>
       </c>
@@ -3745,8 +4306,14 @@
       <c r="F91" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G91" t="s">
+        <v>442</v>
+      </c>
+      <c r="H91" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>92</v>
       </c>
@@ -3765,8 +4332,14 @@
       <c r="F92" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G92" t="s">
+        <v>442</v>
+      </c>
+      <c r="H92" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>93</v>
       </c>
@@ -3777,16 +4350,22 @@
         <v>442</v>
       </c>
       <c r="D93" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E93" t="s">
         <v>442</v>
       </c>
       <c r="F93" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G93" t="s">
+        <v>442</v>
+      </c>
+      <c r="H93" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>94</v>
       </c>
@@ -3797,16 +4376,22 @@
         <v>443</v>
       </c>
       <c r="D94" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E94" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F94" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G94" t="s">
+        <v>444</v>
+      </c>
+      <c r="H94" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>95</v>
       </c>
@@ -3825,8 +4410,14 @@
       <c r="F95" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G95" t="s">
+        <v>444</v>
+      </c>
+      <c r="H95" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>96</v>
       </c>
@@ -3837,16 +4428,22 @@
         <v>443</v>
       </c>
       <c r="D96" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E96" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F96" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G96" t="s">
+        <v>444</v>
+      </c>
+      <c r="H96" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>97</v>
       </c>
@@ -3857,16 +4454,22 @@
         <v>443</v>
       </c>
       <c r="D97" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E97" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F97" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G97" t="s">
+        <v>444</v>
+      </c>
+      <c r="H97" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>98</v>
       </c>
@@ -3877,16 +4480,22 @@
         <v>443</v>
       </c>
       <c r="D98" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E98" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F98" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G98" t="s">
+        <v>444</v>
+      </c>
+      <c r="H98" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>99</v>
       </c>
@@ -3897,16 +4506,22 @@
         <v>442</v>
       </c>
       <c r="D99" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E99" t="s">
         <v>442</v>
       </c>
       <c r="F99" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G99" t="s">
+        <v>442</v>
+      </c>
+      <c r="H99" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>100</v>
       </c>
@@ -3917,16 +4532,22 @@
         <v>442</v>
       </c>
       <c r="D100" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E100" t="s">
         <v>442</v>
       </c>
       <c r="F100" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G100" t="s">
+        <v>442</v>
+      </c>
+      <c r="H100" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>101</v>
       </c>
@@ -3937,16 +4558,22 @@
         <v>443</v>
       </c>
       <c r="D101" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E101" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F101" t="s">
+        <v>444</v>
+      </c>
+      <c r="G101" t="s">
+        <v>442</v>
+      </c>
+      <c r="H101" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>102</v>
       </c>
@@ -3965,8 +4592,14 @@
       <c r="F102" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G102" t="s">
+        <v>444</v>
+      </c>
+      <c r="H102" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>103</v>
       </c>
@@ -3980,13 +4613,19 @@
         <v>444</v>
       </c>
       <c r="E103" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F103" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G103" t="s">
+        <v>443</v>
+      </c>
+      <c r="H103" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>104</v>
       </c>
@@ -4005,8 +4644,14 @@
       <c r="F104" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G104" t="s">
+        <v>442</v>
+      </c>
+      <c r="H104" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>105</v>
       </c>
@@ -4017,16 +4662,22 @@
         <v>443</v>
       </c>
       <c r="D105" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E105" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F105" t="s">
+        <v>444</v>
+      </c>
+      <c r="G105" t="s">
+        <v>442</v>
+      </c>
+      <c r="H105" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>106</v>
       </c>
@@ -4037,16 +4688,22 @@
         <v>442</v>
       </c>
       <c r="D106" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E106" t="s">
         <v>442</v>
       </c>
       <c r="F106" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G106" t="s">
+        <v>442</v>
+      </c>
+      <c r="H106" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>107</v>
       </c>
@@ -4065,8 +4722,14 @@
       <c r="F107" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G107" t="s">
+        <v>442</v>
+      </c>
+      <c r="H107" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>108</v>
       </c>
@@ -4085,8 +4748,14 @@
       <c r="F108" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G108" t="s">
+        <v>442</v>
+      </c>
+      <c r="H108" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>109</v>
       </c>
@@ -4097,16 +4766,22 @@
         <v>443</v>
       </c>
       <c r="D109" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E109" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F109" t="s">
+        <v>444</v>
+      </c>
+      <c r="G109" t="s">
+        <v>442</v>
+      </c>
+      <c r="H109" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>110</v>
       </c>
@@ -4117,16 +4792,22 @@
         <v>443</v>
       </c>
       <c r="D110" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E110" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F110" t="s">
+        <v>444</v>
+      </c>
+      <c r="G110" t="s">
+        <v>442</v>
+      </c>
+      <c r="H110" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>111</v>
       </c>
@@ -4137,16 +4818,22 @@
         <v>443</v>
       </c>
       <c r="D111" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E111" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F111" t="s">
+        <v>444</v>
+      </c>
+      <c r="G111" t="s">
+        <v>442</v>
+      </c>
+      <c r="H111" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>112</v>
       </c>
@@ -4157,16 +4844,22 @@
         <v>442</v>
       </c>
       <c r="D112" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E112" t="s">
         <v>442</v>
       </c>
       <c r="F112" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G112" t="s">
+        <v>442</v>
+      </c>
+      <c r="H112" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>113</v>
       </c>
@@ -4177,16 +4870,22 @@
         <v>443</v>
       </c>
       <c r="D113" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E113" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F113" t="s">
+        <v>444</v>
+      </c>
+      <c r="G113" t="s">
+        <v>442</v>
+      </c>
+      <c r="H113" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>114</v>
       </c>
@@ -4200,13 +4899,19 @@
         <v>443</v>
       </c>
       <c r="E114" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F114" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G114" t="s">
+        <v>442</v>
+      </c>
+      <c r="H114" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>115</v>
       </c>
@@ -4217,16 +4922,22 @@
         <v>442</v>
       </c>
       <c r="D115" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E115" t="s">
         <v>442</v>
       </c>
       <c r="F115" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G115" t="s">
+        <v>442</v>
+      </c>
+      <c r="H115" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>116</v>
       </c>
@@ -4237,16 +4948,22 @@
         <v>442</v>
       </c>
       <c r="D116" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E116" t="s">
         <v>442</v>
       </c>
       <c r="F116" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G116" t="s">
+        <v>442</v>
+      </c>
+      <c r="H116" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>117</v>
       </c>
@@ -4257,16 +4974,22 @@
         <v>442</v>
       </c>
       <c r="D117" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E117" t="s">
         <v>442</v>
       </c>
       <c r="F117" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G117" t="s">
+        <v>442</v>
+      </c>
+      <c r="H117" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>118</v>
       </c>
@@ -4277,16 +5000,22 @@
         <v>443</v>
       </c>
       <c r="D118" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E118" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F118" t="s">
+        <v>444</v>
+      </c>
+      <c r="G118" t="s">
+        <v>442</v>
+      </c>
+      <c r="H118" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>119</v>
       </c>
@@ -4297,16 +5026,22 @@
         <v>442</v>
       </c>
       <c r="D119" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E119" t="s">
         <v>442</v>
       </c>
       <c r="F119" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G119" t="s">
+        <v>442</v>
+      </c>
+      <c r="H119" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>120</v>
       </c>
@@ -4320,13 +5055,19 @@
         <v>444</v>
       </c>
       <c r="E120" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F120" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G120" t="s">
+        <v>443</v>
+      </c>
+      <c r="H120" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>121</v>
       </c>
@@ -4337,16 +5078,22 @@
         <v>443</v>
       </c>
       <c r="D121" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E121" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F121" t="s">
+        <v>444</v>
+      </c>
+      <c r="G121" t="s">
+        <v>442</v>
+      </c>
+      <c r="H121" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>122</v>
       </c>
@@ -4365,8 +5112,14 @@
       <c r="F122" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G122" t="s">
+        <v>442</v>
+      </c>
+      <c r="H122" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>123</v>
       </c>
@@ -4377,16 +5130,22 @@
         <v>443</v>
       </c>
       <c r="D123" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E123" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F123" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G123" t="s">
+        <v>444</v>
+      </c>
+      <c r="H123" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>124</v>
       </c>
@@ -4397,16 +5156,22 @@
         <v>443</v>
       </c>
       <c r="D124" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E124" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F124" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G124" t="s">
+        <v>444</v>
+      </c>
+      <c r="H124" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>125</v>
       </c>
@@ -4417,16 +5182,22 @@
         <v>442</v>
       </c>
       <c r="D125" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E125" t="s">
         <v>442</v>
       </c>
       <c r="F125" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G125" t="s">
+        <v>442</v>
+      </c>
+      <c r="H125" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>126</v>
       </c>
@@ -4437,16 +5208,22 @@
         <v>443</v>
       </c>
       <c r="D126" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E126" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F126" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G126" t="s">
+        <v>444</v>
+      </c>
+      <c r="H126" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>127</v>
       </c>
@@ -4457,16 +5234,22 @@
         <v>443</v>
       </c>
       <c r="D127" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E127" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F127" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G127" t="s">
+        <v>444</v>
+      </c>
+      <c r="H127" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>128</v>
       </c>
@@ -4477,16 +5260,22 @@
         <v>443</v>
       </c>
       <c r="D128" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E128" t="s">
         <v>443</v>
       </c>
       <c r="F128" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G128" t="s">
+        <v>443</v>
+      </c>
+      <c r="H128" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>129</v>
       </c>
@@ -4497,16 +5286,22 @@
         <v>443</v>
       </c>
       <c r="D129" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E129" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F129" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G129" t="s">
+        <v>444</v>
+      </c>
+      <c r="H129" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>130</v>
       </c>
@@ -4525,8 +5320,14 @@
       <c r="F130" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G130" t="s">
+        <v>442</v>
+      </c>
+      <c r="H130" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>131</v>
       </c>
@@ -4537,16 +5338,22 @@
         <v>443</v>
       </c>
       <c r="D131" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E131" t="s">
         <v>443</v>
       </c>
       <c r="F131" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G131" t="s">
+        <v>443</v>
+      </c>
+      <c r="H131" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>132</v>
       </c>
@@ -4557,16 +5364,22 @@
         <v>442</v>
       </c>
       <c r="D132" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E132" t="s">
         <v>442</v>
       </c>
       <c r="F132" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G132" t="s">
+        <v>442</v>
+      </c>
+      <c r="H132" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>133</v>
       </c>
@@ -4577,16 +5390,22 @@
         <v>443</v>
       </c>
       <c r="D133" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E133" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F133" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G133" t="s">
+        <v>444</v>
+      </c>
+      <c r="H133" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>134</v>
       </c>
@@ -4597,16 +5416,22 @@
         <v>443</v>
       </c>
       <c r="D134" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E134" t="s">
         <v>443</v>
       </c>
       <c r="F134" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G134" t="s">
+        <v>443</v>
+      </c>
+      <c r="H134" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>135</v>
       </c>
@@ -4617,16 +5442,22 @@
         <v>443</v>
       </c>
       <c r="D135" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E135" t="s">
         <v>443</v>
       </c>
       <c r="F135" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G135" t="s">
+        <v>443</v>
+      </c>
+      <c r="H135" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>136</v>
       </c>
@@ -4637,16 +5468,22 @@
         <v>442</v>
       </c>
       <c r="D136" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E136" t="s">
         <v>442</v>
       </c>
       <c r="F136" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G136" t="s">
+        <v>442</v>
+      </c>
+      <c r="H136" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>137</v>
       </c>
@@ -4665,8 +5502,14 @@
       <c r="F137" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G137" t="s">
+        <v>444</v>
+      </c>
+      <c r="H137" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>138</v>
       </c>
@@ -4677,16 +5520,22 @@
         <v>443</v>
       </c>
       <c r="D138" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E138" t="s">
         <v>443</v>
       </c>
       <c r="F138" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+        <v>442</v>
+      </c>
+      <c r="G138" t="s">
+        <v>443</v>
+      </c>
+      <c r="H138" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>139</v>
       </c>
@@ -4705,8 +5554,14 @@
       <c r="F139" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G139" t="s">
+        <v>442</v>
+      </c>
+      <c r="H139" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>140</v>
       </c>
@@ -4717,16 +5572,22 @@
         <v>442</v>
       </c>
       <c r="D140" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E140" t="s">
         <v>442</v>
       </c>
       <c r="F140" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G140" t="s">
+        <v>442</v>
+      </c>
+      <c r="H140" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>141</v>
       </c>
@@ -4737,16 +5598,22 @@
         <v>443</v>
       </c>
       <c r="D141" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E141" t="s">
         <v>443</v>
       </c>
       <c r="F141" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G141" t="s">
+        <v>443</v>
+      </c>
+      <c r="H141" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>142</v>
       </c>
@@ -4757,16 +5624,22 @@
         <v>443</v>
       </c>
       <c r="D142" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E142" t="s">
         <v>443</v>
       </c>
       <c r="F142" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G142" t="s">
+        <v>443</v>
+      </c>
+      <c r="H142" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>143</v>
       </c>
@@ -4785,8 +5658,14 @@
       <c r="F143" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G143" t="s">
+        <v>442</v>
+      </c>
+      <c r="H143" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>144</v>
       </c>
@@ -4797,16 +5676,22 @@
         <v>443</v>
       </c>
       <c r="D144" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E144" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F144" t="s">
+        <v>444</v>
+      </c>
+      <c r="G144" t="s">
+        <v>442</v>
+      </c>
+      <c r="H144" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>145</v>
       </c>
@@ -4825,8 +5710,14 @@
       <c r="F145" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G145" t="s">
+        <v>442</v>
+      </c>
+      <c r="H145" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>146</v>
       </c>
@@ -4837,16 +5728,22 @@
         <v>442</v>
       </c>
       <c r="D146" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E146" t="s">
         <v>442</v>
       </c>
       <c r="F146" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G146" t="s">
+        <v>442</v>
+      </c>
+      <c r="H146" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>147</v>
       </c>
@@ -4865,8 +5762,14 @@
       <c r="F147" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G147" t="s">
+        <v>442</v>
+      </c>
+      <c r="H147" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>148</v>
       </c>
@@ -4877,16 +5780,22 @@
         <v>442</v>
       </c>
       <c r="D148" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E148" t="s">
         <v>442</v>
       </c>
       <c r="F148" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G148" t="s">
+        <v>442</v>
+      </c>
+      <c r="H148" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>149</v>
       </c>
@@ -4900,13 +5809,19 @@
         <v>444</v>
       </c>
       <c r="E149" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F149" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G149" t="s">
+        <v>443</v>
+      </c>
+      <c r="H149" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>150</v>
       </c>
@@ -4925,8 +5840,14 @@
       <c r="F150" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G150" t="s">
+        <v>442</v>
+      </c>
+      <c r="H150" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>151</v>
       </c>
@@ -4937,16 +5858,22 @@
         <v>442</v>
       </c>
       <c r="D151" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E151" t="s">
         <v>442</v>
       </c>
       <c r="F151" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G151" t="s">
+        <v>442</v>
+      </c>
+      <c r="H151" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>152</v>
       </c>
@@ -4957,16 +5884,22 @@
         <v>443</v>
       </c>
       <c r="D152" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E152" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F152" t="s">
+        <v>444</v>
+      </c>
+      <c r="G152" t="s">
+        <v>442</v>
+      </c>
+      <c r="H152" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>153</v>
       </c>
@@ -4985,8 +5918,14 @@
       <c r="F153" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G153" t="s">
+        <v>442</v>
+      </c>
+      <c r="H153" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>154</v>
       </c>
@@ -5005,8 +5944,14 @@
       <c r="F154" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G154" t="s">
+        <v>442</v>
+      </c>
+      <c r="H154" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>155</v>
       </c>
@@ -5017,16 +5962,22 @@
         <v>442</v>
       </c>
       <c r="D155" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E155" t="s">
         <v>442</v>
       </c>
       <c r="F155" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G155" t="s">
+        <v>442</v>
+      </c>
+      <c r="H155" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>156</v>
       </c>
@@ -5045,8 +5996,14 @@
       <c r="F156" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G156" t="s">
+        <v>442</v>
+      </c>
+      <c r="H156" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>157</v>
       </c>
@@ -5060,13 +6017,19 @@
         <v>443</v>
       </c>
       <c r="E157" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F157" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G157" t="s">
+        <v>442</v>
+      </c>
+      <c r="H157" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>158</v>
       </c>
@@ -5085,8 +6048,14 @@
       <c r="F158" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G158" t="s">
+        <v>442</v>
+      </c>
+      <c r="H158" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>159</v>
       </c>
@@ -5105,8 +6074,14 @@
       <c r="F159" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G159" t="s">
+        <v>444</v>
+      </c>
+      <c r="H159" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>160</v>
       </c>
@@ -5117,16 +6092,22 @@
         <v>442</v>
       </c>
       <c r="D160" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E160" t="s">
         <v>442</v>
       </c>
       <c r="F160" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G160" t="s">
+        <v>442</v>
+      </c>
+      <c r="H160" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>161</v>
       </c>
@@ -5137,16 +6118,22 @@
         <v>443</v>
       </c>
       <c r="D161" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E161" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F161" t="s">
+        <v>444</v>
+      </c>
+      <c r="G161" t="s">
+        <v>442</v>
+      </c>
+      <c r="H161" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>162</v>
       </c>
@@ -5157,16 +6144,22 @@
         <v>442</v>
       </c>
       <c r="D162" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E162" t="s">
         <v>442</v>
       </c>
       <c r="F162" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G162" t="s">
+        <v>442</v>
+      </c>
+      <c r="H162" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>163</v>
       </c>
@@ -5185,8 +6178,14 @@
       <c r="F163" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G163" t="s">
+        <v>442</v>
+      </c>
+      <c r="H163" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>164</v>
       </c>
@@ -5197,16 +6196,22 @@
         <v>443</v>
       </c>
       <c r="D164" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E164" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F164" t="s">
+        <v>444</v>
+      </c>
+      <c r="G164" t="s">
+        <v>442</v>
+      </c>
+      <c r="H164" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>165</v>
       </c>
@@ -5217,16 +6222,22 @@
         <v>442</v>
       </c>
       <c r="D165" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E165" t="s">
         <v>442</v>
       </c>
       <c r="F165" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G165" t="s">
+        <v>442</v>
+      </c>
+      <c r="H165" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>166</v>
       </c>
@@ -5237,16 +6248,22 @@
         <v>443</v>
       </c>
       <c r="D166" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E166" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F166" t="s">
+        <v>444</v>
+      </c>
+      <c r="G166" t="s">
+        <v>442</v>
+      </c>
+      <c r="H166" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>167</v>
       </c>
@@ -5257,16 +6274,22 @@
         <v>442</v>
       </c>
       <c r="D167" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E167" t="s">
         <v>442</v>
       </c>
       <c r="F167" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G167" t="s">
+        <v>442</v>
+      </c>
+      <c r="H167" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>168</v>
       </c>
@@ -5280,13 +6303,19 @@
         <v>444</v>
       </c>
       <c r="E168" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F168" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G168" t="s">
+        <v>443</v>
+      </c>
+      <c r="H168" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>169</v>
       </c>
@@ -5297,16 +6326,22 @@
         <v>442</v>
       </c>
       <c r="D169" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E169" t="s">
         <v>442</v>
       </c>
       <c r="F169" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G169" t="s">
+        <v>442</v>
+      </c>
+      <c r="H169" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>170</v>
       </c>
@@ -5325,8 +6360,14 @@
       <c r="F170" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G170" t="s">
+        <v>442</v>
+      </c>
+      <c r="H170" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>171</v>
       </c>
@@ -5345,8 +6386,14 @@
       <c r="F171" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G171" t="s">
+        <v>442</v>
+      </c>
+      <c r="H171" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>172</v>
       </c>
@@ -5357,16 +6404,22 @@
         <v>442</v>
       </c>
       <c r="D172" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E172" t="s">
         <v>442</v>
       </c>
       <c r="F172" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G172" t="s">
+        <v>442</v>
+      </c>
+      <c r="H172" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>173</v>
       </c>
@@ -5377,16 +6430,22 @@
         <v>442</v>
       </c>
       <c r="D173" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E173" t="s">
         <v>442</v>
       </c>
       <c r="F173" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G173" t="s">
+        <v>442</v>
+      </c>
+      <c r="H173" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>174</v>
       </c>
@@ -5405,8 +6464,14 @@
       <c r="F174" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G174" t="s">
+        <v>442</v>
+      </c>
+      <c r="H174" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>175</v>
       </c>
@@ -5417,16 +6482,22 @@
         <v>442</v>
       </c>
       <c r="D175" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E175" t="s">
         <v>442</v>
       </c>
       <c r="F175" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G175" t="s">
+        <v>442</v>
+      </c>
+      <c r="H175" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>176</v>
       </c>
@@ -5437,16 +6508,22 @@
         <v>442</v>
       </c>
       <c r="D176" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E176" t="s">
         <v>442</v>
       </c>
       <c r="F176" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G176" t="s">
+        <v>442</v>
+      </c>
+      <c r="H176" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>177</v>
       </c>
@@ -5457,16 +6534,22 @@
         <v>442</v>
       </c>
       <c r="D177" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E177" t="s">
         <v>442</v>
       </c>
       <c r="F177" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G177" t="s">
+        <v>442</v>
+      </c>
+      <c r="H177" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>178</v>
       </c>
@@ -5485,8 +6568,14 @@
       <c r="F178" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G178" t="s">
+        <v>444</v>
+      </c>
+      <c r="H178" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>179</v>
       </c>
@@ -5497,16 +6586,22 @@
         <v>443</v>
       </c>
       <c r="D179" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E179" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F179" t="s">
+        <v>444</v>
+      </c>
+      <c r="G179" t="s">
+        <v>442</v>
+      </c>
+      <c r="H179" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>180</v>
       </c>
@@ -5517,16 +6612,22 @@
         <v>443</v>
       </c>
       <c r="D180" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F180" t="s">
+        <v>444</v>
+      </c>
+      <c r="G180" t="s">
+        <v>442</v>
+      </c>
+      <c r="H180" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>181</v>
       </c>
@@ -5545,8 +6646,14 @@
       <c r="F181" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G181" t="s">
+        <v>442</v>
+      </c>
+      <c r="H181" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>182</v>
       </c>
@@ -5557,16 +6664,22 @@
         <v>442</v>
       </c>
       <c r="D182" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E182" t="s">
         <v>442</v>
       </c>
       <c r="F182" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G182" t="s">
+        <v>442</v>
+      </c>
+      <c r="H182" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>183</v>
       </c>
@@ -5577,16 +6690,22 @@
         <v>443</v>
       </c>
       <c r="D183" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E183" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F183" t="s">
+        <v>444</v>
+      </c>
+      <c r="G183" t="s">
+        <v>442</v>
+      </c>
+      <c r="H183" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>184</v>
       </c>
@@ -5597,16 +6716,22 @@
         <v>443</v>
       </c>
       <c r="D184" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E184" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F184" t="s">
+        <v>444</v>
+      </c>
+      <c r="G184" t="s">
+        <v>442</v>
+      </c>
+      <c r="H184" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>185</v>
       </c>
@@ -5625,8 +6750,14 @@
       <c r="F185" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G185" t="s">
+        <v>442</v>
+      </c>
+      <c r="H185" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>186</v>
       </c>
@@ -5640,13 +6771,19 @@
         <v>444</v>
       </c>
       <c r="E186" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F186" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G186" t="s">
+        <v>443</v>
+      </c>
+      <c r="H186" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>187</v>
       </c>
@@ -5665,8 +6802,14 @@
       <c r="F187" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G187" t="s">
+        <v>442</v>
+      </c>
+      <c r="H187" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>188</v>
       </c>
@@ -5680,13 +6823,19 @@
         <v>444</v>
       </c>
       <c r="E188" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F188" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G188" t="s">
+        <v>443</v>
+      </c>
+      <c r="H188" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>189</v>
       </c>
@@ -5705,8 +6854,14 @@
       <c r="F189" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G189" t="s">
+        <v>442</v>
+      </c>
+      <c r="H189" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>190</v>
       </c>
@@ -5725,8 +6880,14 @@
       <c r="F190" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G190" t="s">
+        <v>442</v>
+      </c>
+      <c r="H190" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>191</v>
       </c>
@@ -5740,13 +6901,19 @@
         <v>444</v>
       </c>
       <c r="E191" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F191" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G191" t="s">
+        <v>443</v>
+      </c>
+      <c r="H191" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>192</v>
       </c>
@@ -5757,16 +6924,22 @@
         <v>443</v>
       </c>
       <c r="D192" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E192" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F192" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G192" t="s">
+        <v>444</v>
+      </c>
+      <c r="H192" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>193</v>
       </c>
@@ -5774,7 +6947,7 @@
         <v>413</v>
       </c>
       <c r="C193" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D193" t="s">
         <v>442</v>
@@ -5785,8 +6958,14 @@
       <c r="F193" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G193" t="s">
+        <v>442</v>
+      </c>
+      <c r="H193" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>194</v>
       </c>
@@ -5797,16 +6976,22 @@
         <v>442</v>
       </c>
       <c r="D194" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E194" t="s">
         <v>442</v>
       </c>
       <c r="F194" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G194" t="s">
+        <v>442</v>
+      </c>
+      <c r="H194" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>195</v>
       </c>
@@ -5817,16 +7002,22 @@
         <v>442</v>
       </c>
       <c r="D195" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E195" t="s">
         <v>442</v>
       </c>
       <c r="F195" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G195" t="s">
+        <v>442</v>
+      </c>
+      <c r="H195" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>196</v>
       </c>
@@ -5837,16 +7028,22 @@
         <v>442</v>
       </c>
       <c r="D196" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E196" t="s">
         <v>442</v>
       </c>
       <c r="F196" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G196" t="s">
+        <v>442</v>
+      </c>
+      <c r="H196" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>197</v>
       </c>
@@ -5857,16 +7054,22 @@
         <v>442</v>
       </c>
       <c r="D197" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E197" t="s">
         <v>442</v>
       </c>
       <c r="F197" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G197" t="s">
+        <v>442</v>
+      </c>
+      <c r="H197" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>198</v>
       </c>
@@ -5877,16 +7080,22 @@
         <v>442</v>
       </c>
       <c r="D198" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E198" t="s">
         <v>442</v>
       </c>
       <c r="F198" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G198" t="s">
+        <v>442</v>
+      </c>
+      <c r="H198" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>199</v>
       </c>
@@ -5897,16 +7106,22 @@
         <v>443</v>
       </c>
       <c r="D199" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E199" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F199" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G199" t="s">
+        <v>444</v>
+      </c>
+      <c r="H199" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>200</v>
       </c>
@@ -5925,8 +7140,14 @@
       <c r="F200" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G200" t="s">
+        <v>442</v>
+      </c>
+      <c r="H200" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>201</v>
       </c>
@@ -5945,8 +7166,14 @@
       <c r="F201" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G201" t="s">
+        <v>444</v>
+      </c>
+      <c r="H201" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>202</v>
       </c>
@@ -5965,8 +7192,14 @@
       <c r="F202" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G202" t="s">
+        <v>444</v>
+      </c>
+      <c r="H202" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>203</v>
       </c>
@@ -5977,16 +7210,22 @@
         <v>443</v>
       </c>
       <c r="D203" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E203" t="s">
         <v>443</v>
       </c>
       <c r="F203" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G203" t="s">
+        <v>443</v>
+      </c>
+      <c r="H203" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>204</v>
       </c>
@@ -5994,19 +7233,25 @@
         <v>424</v>
       </c>
       <c r="C204" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D204" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E204" t="s">
         <v>442</v>
       </c>
       <c r="F204" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G204" t="s">
+        <v>442</v>
+      </c>
+      <c r="H204" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>205</v>
       </c>
@@ -6017,16 +7262,22 @@
         <v>443</v>
       </c>
       <c r="D205" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E205" t="s">
         <v>443</v>
       </c>
       <c r="F205" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G205" t="s">
+        <v>443</v>
+      </c>
+      <c r="H205" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>206</v>
       </c>
@@ -6040,13 +7291,19 @@
         <v>443</v>
       </c>
       <c r="E206" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F206" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G206" t="s">
+        <v>442</v>
+      </c>
+      <c r="H206" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>207</v>
       </c>
@@ -6065,8 +7322,14 @@
       <c r="F207" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G207" t="s">
+        <v>442</v>
+      </c>
+      <c r="H207" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>208</v>
       </c>
@@ -6080,13 +7343,19 @@
         <v>444</v>
       </c>
       <c r="E208" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F208" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G208" t="s">
+        <v>443</v>
+      </c>
+      <c r="H208" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>209</v>
       </c>
@@ -6097,16 +7366,22 @@
         <v>443</v>
       </c>
       <c r="D209" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E209" t="s">
         <v>443</v>
       </c>
       <c r="F209" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G209" t="s">
+        <v>443</v>
+      </c>
+      <c r="H209" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>210</v>
       </c>
@@ -6120,13 +7395,19 @@
         <v>444</v>
       </c>
       <c r="E210" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F210" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G210" t="s">
+        <v>443</v>
+      </c>
+      <c r="H210" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>211</v>
       </c>
@@ -6137,16 +7418,22 @@
         <v>442</v>
       </c>
       <c r="D211" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E211" t="s">
         <v>442</v>
       </c>
       <c r="F211" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="G211" t="s">
+        <v>442</v>
+      </c>
+      <c r="H211" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>212</v>
       </c>
@@ -6165,8 +7452,14 @@
       <c r="F212" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G212" t="s">
+        <v>442</v>
+      </c>
+      <c r="H212" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>213</v>
       </c>
@@ -6174,7 +7467,7 @@
         <v>433</v>
       </c>
       <c r="C213" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D213" t="s">
         <v>442</v>
@@ -6185,8 +7478,14 @@
       <c r="F213" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G213" t="s">
+        <v>442</v>
+      </c>
+      <c r="H213" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>214</v>
       </c>
@@ -6200,13 +7499,19 @@
         <v>444</v>
       </c>
       <c r="E214" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F214" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G214" t="s">
+        <v>443</v>
+      </c>
+      <c r="H214" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>215</v>
       </c>
@@ -6220,13 +7525,19 @@
         <v>444</v>
       </c>
       <c r="E215" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F215" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G215" t="s">
+        <v>443</v>
+      </c>
+      <c r="H215" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>216</v>
       </c>
@@ -6237,16 +7548,22 @@
         <v>443</v>
       </c>
       <c r="D216" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E216" t="s">
         <v>443</v>
       </c>
       <c r="F216" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+      <c r="G216" t="s">
+        <v>443</v>
+      </c>
+      <c r="H216" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>217</v>
       </c>
@@ -6257,16 +7574,22 @@
         <v>443</v>
       </c>
       <c r="D217" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E217" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F217" t="s">
+        <v>444</v>
+      </c>
+      <c r="G217" t="s">
+        <v>442</v>
+      </c>
+      <c r="H217" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>218</v>
       </c>
@@ -6280,13 +7603,19 @@
         <v>444</v>
       </c>
       <c r="E218" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F218" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G218" t="s">
+        <v>443</v>
+      </c>
+      <c r="H218" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>219</v>
       </c>
@@ -6300,13 +7629,19 @@
         <v>444</v>
       </c>
       <c r="E219" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F219" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G219" t="s">
+        <v>443</v>
+      </c>
+      <c r="H219" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>220</v>
       </c>
@@ -6320,13 +7655,19 @@
         <v>444</v>
       </c>
       <c r="E220" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F220" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G220" t="s">
+        <v>443</v>
+      </c>
+      <c r="H220" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>221</v>
       </c>
@@ -6340,9 +7681,15 @@
         <v>444</v>
       </c>
       <c r="E221" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F221" t="s">
+        <v>444</v>
+      </c>
+      <c r="G221" t="s">
+        <v>443</v>
+      </c>
+      <c r="H221" t="s">
         <v>444</v>
       </c>
     </row>
